--- a/Plots/Dominant Tree_Species_Plot.xlsx
+++ b/Plots/Dominant Tree_Species_Plot.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\gumbo_dev\Plots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE4154F-96BF-4CB5-A4ED-BFD13039A8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCBB8F1-AA19-4899-87F8-564B53608EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -453,9 +466,10 @@
     <col min="2" max="2" width="7.54296875" customWidth="1"/>
     <col min="3" max="3" width="19.453125" customWidth="1"/>
     <col min="4" max="4" width="14.6328125" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" customWidth="1"/>
     <col min="6" max="6" width="15.1796875" customWidth="1"/>
     <col min="7" max="7" width="15.7265625" customWidth="1"/>
+    <col min="8" max="8" width="14.453125" customWidth="1"/>
     <col min="9" max="9" width="13.36328125" customWidth="1"/>
     <col min="13" max="13" width="12.08984375" customWidth="1"/>
   </cols>
